--- a/network-contacts-template.xlsx
+++ b/network-contacts-template.xlsx
@@ -399,14 +399,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H11"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="36.83203125" customWidth="1"/>
+    <col min="5" max="5" width="32.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="42.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="36.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +426,10 @@
         <v>contact_value</v>
       </c>
       <c r="F1" t="str">
+        <v>connected_date</v>
+      </c>
+      <c r="G1" t="str">
         <v>last_contact</v>
-      </c>
-      <c r="G1" t="str">
-        <v>next_follow_up</v>
       </c>
       <c r="H1" t="str">
         <v>reminder_note</v>
@@ -452,10 +452,10 @@
         <v>linkedin.com/in/janesmith</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-03-15</v>
+        <v>2026-01-10</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-05-10</v>
+        <v>2026-04-15</v>
       </c>
       <c r="H2" t="str">
         <v>Ask about eng openings</v>
@@ -478,10 +478,10 @@
         <v>john.doe@openai.com</v>
       </c>
       <c r="F3" t="str">
-        <v>2025-04-01</v>
+        <v>2026-02-03</v>
       </c>
       <c r="G3" t="str">
-        <v>2025-05-20</v>
+        <v>2026-04-01</v>
       </c>
       <c r="H3" t="str">
         <v>Referred by Jane — follow up on ML role</v>
@@ -504,10 +504,10 @@
         <v>555-867-5309</v>
       </c>
       <c r="F4" t="str">
-        <v>2025-02-20</v>
+        <v>2025-11-20</v>
       </c>
       <c r="G4" t="str">
-        <v>2025-04-30</v>
+        <v>2026-02-20</v>
       </c>
       <c r="H4" t="str">
         <v>Coffee chat, strong connection</v>
@@ -530,10 +530,10 @@
         <v>linkedin.com/in/marcust</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>2026-03-15</v>
       </c>
       <c r="G5" t="str">
-        <v>2025-06-01</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>Met at React conf</v>
@@ -556,10 +556,10 @@
         <v>priya@anthropic.com</v>
       </c>
       <c r="F6" t="str">
-        <v>2025-04-10</v>
+        <v>2026-04-01</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>2026-04-10</v>
       </c>
       <c r="H6" t="str">
         <v>Informational interview done</v>
@@ -582,10 +582,10 @@
         <v>@alexr on Slack</v>
       </c>
       <c r="F7" t="str">
-        <v>2025-03-01</v>
+        <v>2026-03-01</v>
       </c>
       <c r="G7" t="str">
-        <v>2025-05-15</v>
+        <v>2026-04-28</v>
       </c>
       <c r="H7" t="str">
         <v>Slack contact from hackathon</v>
@@ -640,12 +640,59 @@
         <v/>
       </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>contact_method values: linkedin | email | phone | other</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/network-contacts-template.xlsx
+++ b/network-contacts-template.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Contacts" sheetId="1" r:id="rId1"/>
+    <sheet name="Legend" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,16 +398,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J3"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="36.83203125" customWidth="1"/>
+    <col min="7" max="7" width="36.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="36.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -414,24 +417,30 @@
         <v>name</v>
       </c>
       <c r="B1" t="str">
+        <v>contact_category</v>
+      </c>
+      <c r="C1" t="str">
         <v>company</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>relationship</v>
+      </c>
+      <c r="E1" t="str">
         <v>location</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>contact_method</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>contact_value</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>connected_date</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>last_contact</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>reminder_note</v>
       </c>
     </row>
@@ -440,25 +449,31 @@
         <v>Jane Smith</v>
       </c>
       <c r="B2" t="str">
+        <v>professional</v>
+      </c>
+      <c r="C2" t="str">
         <v>Acme Corp</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
         <v>San Francisco, CA</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
         <v>linkedin</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <v>linkedin.com/in/janesmith</v>
       </c>
-      <c r="F2" t="str">
-        <v>2026-01-10</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-04-15</v>
-      </c>
       <c r="H2" t="str">
-        <v>Ask about eng openings</v>
+        <v>2025-01-15</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Follow up on roadmap discussion</v>
       </c>
     </row>
     <row r="3">
@@ -466,238 +481,173 @@
         <v>John Doe</v>
       </c>
       <c r="B3" t="str">
-        <v>OpenAI</v>
+        <v>personal</v>
       </c>
       <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>Friend</v>
+      </c>
+      <c r="E3" t="str">
         <v>New York, NY</v>
       </c>
-      <c r="D3" t="str">
+      <c r="F3" t="str">
         <v>email</v>
       </c>
-      <c r="E3" t="str">
-        <v>john.doe@openai.com</v>
-      </c>
-      <c r="F3" t="str">
-        <v>2026-02-03</v>
-      </c>
       <c r="G3" t="str">
-        <v>2026-04-01</v>
+        <v>john@example.com</v>
       </c>
       <c r="H3" t="str">
-        <v>Referred by Jane — follow up on ML role</v>
+        <v>2024-06-01</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Coffee meetup</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C11"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="85.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Column</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Required?</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Allowed Values / Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>name</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Full name of the contact</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>contact_category</v>
+      </c>
+      <c r="B3" t="str">
+        <v>No</v>
+      </c>
+      <c r="C3" t="str">
+        <v>professional (default) | personal</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sarah Lee</v>
+        <v>company</v>
       </c>
       <c r="B4" t="str">
-        <v>Google</v>
+        <v>No</v>
       </c>
       <c r="C4" t="str">
-        <v>Seattle, WA</v>
-      </c>
-      <c r="D4" t="str">
-        <v>phone</v>
-      </c>
-      <c r="E4" t="str">
-        <v>555-867-5309</v>
-      </c>
-      <c r="F4" t="str">
-        <v>2025-11-20</v>
-      </c>
-      <c r="G4" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Coffee chat, strong connection</v>
+        <v>Employer — use for professional contacts</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Marcus T.</v>
+        <v>relationship</v>
       </c>
       <c r="B5" t="str">
-        <v>Stripe</v>
+        <v>No</v>
       </c>
       <c r="C5" t="str">
-        <v>Remote</v>
-      </c>
-      <c r="D5" t="str">
-        <v>linkedin</v>
-      </c>
-      <c r="E5" t="str">
-        <v>linkedin.com/in/marcust</v>
-      </c>
-      <c r="F5" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v>Met at React conf</v>
+        <v>Family | Friend | Partner | Mentor | Mentee | Classmate | Neighbor | Acquaintance | Other — sets category to personal automatically</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Priya K.</v>
+        <v>location</v>
       </c>
       <c r="B6" t="str">
-        <v>Anthropic</v>
+        <v>No</v>
       </c>
       <c r="C6" t="str">
-        <v>San Francisco, CA</v>
-      </c>
-      <c r="D6" t="str">
-        <v>email</v>
-      </c>
-      <c r="E6" t="str">
-        <v>priya@anthropic.com</v>
-      </c>
-      <c r="F6" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2026-04-10</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Informational interview done</v>
+        <v>City, State / Country</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Alex R.</v>
+        <v>contact_method</v>
       </c>
       <c r="B7" t="str">
-        <v>Meta</v>
+        <v>No</v>
       </c>
       <c r="C7" t="str">
-        <v>Austin, TX</v>
-      </c>
-      <c r="D7" t="str">
-        <v>other</v>
-      </c>
-      <c r="E7" t="str">
-        <v>@alexr on Slack</v>
-      </c>
-      <c r="F7" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="G7" t="str">
-        <v>2026-04-28</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Slack contact from hackathon</v>
+        <v>linkedin (default) | email | phone | other</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>contact_value</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
+        <v>LinkedIn URL, email address, phone number, etc.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>connected_date</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
+        <v>YYYY-MM-DD or MM/DD/YYYY — when you first connected</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>last_contact</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
+        <v>YYYY-MM-DD or MM/DD/YYYY — most recent interaction</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>contact_method values: linkedin | email | phone | other</v>
+        <v>reminder_note</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>No</v>
       </c>
       <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
+        <v>Notes or reminder for next follow-up</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>